--- a/jogos_2025-10-11.xlsx
+++ b/jogos_2025-10-11.xlsx
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,14 +6603,14 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="M48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.7</v>
       </c>
-      <c r="N48" t="n">
-        <v>5.25</v>
-      </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,61 +15246,61 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,16 +15414,16 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,16 +16317,16 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>

--- a/jogos_2025-10-11.xlsx
+++ b/jogos_2025-10-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45941.39583333334</v>
+        <v>45941.375</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45941.39583333334</v>
+        <v>45941.375</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45941.41666666666</v>
+        <v>45941.39583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45941.41666666666</v>
+        <v>45941.39583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.41666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.41666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.41666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
         <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5703,10 +5703,10 @@
         <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N60" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N61" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9271,27 +9271,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45941.47916666666</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.47916666666</v>
       </c>
     </row>
     <row r="76">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="81">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="83">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="85">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="86">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45941.53125</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45941.54166666666</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45941.55208333334</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,27 +11980,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.53125</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45941.57291666666</v>
+        <v>45941.54166666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45941.58333333334</v>
+        <v>45941.55208333334</v>
       </c>
     </row>
     <row r="95">
@@ -12625,27 +12625,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45941.625</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45941.70833333334</v>
+        <v>45941.57291666666</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45941.72916666666</v>
+        <v>45941.58333333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45941.75</v>
+        <v>45941.625</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.70833333334</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.72916666666</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.75</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,61 +15246,61 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="AG115" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,16 +15414,16 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="118">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45941.875</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45941.91666666666</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45941.9375</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45941.95833333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45941.97916666666</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,126 +16237,900 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
+        <v>45941.85416666666</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK124" s="3" t="n">
+        <v>45941.875</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
+        <v>45941.91666666666</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="3" t="n">
+        <v>45941.9375</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" s="3" t="n">
+        <v>45941.95833333334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>FC Dallas</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L123" t="n">
+      <c r="L128" t="n">
         <v>1.65</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M128" t="n">
         <v>3.85</v>
       </c>
-      <c r="N123" t="n">
+      <c r="N128" t="n">
         <v>4.7</v>
       </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z123" t="n">
+      <c r="Z128" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA123" t="n">
+      <c r="AA128" t="n">
         <v>2.16</v>
       </c>
-      <c r="AB123" t="n">
+      <c r="AB128" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3" t="n">
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" s="3" t="n">
+        <v>45941.97916666666</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" s="3" t="n">
         <v>45941.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-11.xlsx
+++ b/jogos_2025-10-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK129"/>
+  <dimension ref="A1:AK128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>2.09</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>2.26</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="N56" t="n">
-        <v>2.25</v>
+        <v>2.91</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.05</v>
+        <v>2.17</v>
       </c>
       <c r="M60" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="N60" t="n">
-        <v>1.75</v>
+        <v>2.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="M61" t="n">
-        <v>3.7</v>
+        <v>3.33</v>
       </c>
       <c r="N61" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="M65" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N65" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.45</v>
+        <v>3.47</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45941.625</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.70833333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45941.70833333334</v>
+        <v>45941.72916666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45941.72916666666</v>
+        <v>45941.75</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45941.75</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="108">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="114">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="119">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.875</v>
       </c>
     </row>
     <row r="124">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45941.875</v>
+        <v>45941.91666666666</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45941.91666666666</v>
+        <v>45941.9375</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45941.9375</v>
+        <v>45941.95833333334</v>
       </c>
     </row>
     <row r="127">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45941.95833333334</v>
+        <v>45941.97916666666</v>
       </c>
     </row>
     <row r="128">
@@ -17002,135 +17002,6 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45941.97916666666</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" s="3" t="n">
         <v>45941.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-11.xlsx
+++ b/jogos_2025-10-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK128"/>
+  <dimension ref="A1:AK123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45941.35416666666</v>
+        <v>45941.375</v>
       </c>
     </row>
     <row r="12">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45941.375</v>
+        <v>45941.39583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45941.39583333334</v>
+        <v>45941.41666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45941.41666666666</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.03</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.84</v>
+        <v>1.96</v>
       </c>
       <c r="M46" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.27</v>
+        <v>3.47</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="M48" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.21</v>
+        <v>4.5</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.47</v>
+        <v>2.29</v>
       </c>
       <c r="M51" t="n">
-        <v>3.72</v>
+        <v>3.23</v>
       </c>
       <c r="N51" t="n">
-        <v>5.8</v>
+        <v>2.68</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N53" t="n">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.03</v>
+        <v>2.86</v>
       </c>
       <c r="M54" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N54" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>2.03</v>
       </c>
       <c r="M55" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="M57" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="N57" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4.4</v>
+        <v>1.47</v>
       </c>
       <c r="M58" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="N58" t="n">
-        <v>1.61</v>
+        <v>5.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="M59" t="n">
         <v>3.37</v>
       </c>
       <c r="N59" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="M60" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="N61" t="n">
-        <v>3.35</v>
+        <v>3.87</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.57</v>
+        <v>1.83</v>
       </c>
       <c r="M64" t="n">
-        <v>3.02</v>
+        <v>3.37</v>
       </c>
       <c r="N64" t="n">
-        <v>2.5</v>
+        <v>3.62</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.84</v>
+        <v>2.84</v>
       </c>
       <c r="M65" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="N65" t="n">
-        <v>3.62</v>
+        <v>2.27</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N67" t="n">
-        <v>3.47</v>
+        <v>2.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.47916666666</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45941.47916666666</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="76">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="83">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="85">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="86">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.53125</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.54166666666</v>
       </c>
     </row>
     <row r="90">
@@ -11980,27 +11980,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45941.53125</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45941.54166666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45941.55208333334</v>
+        <v>45941.57291666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.58333333334</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45941.57291666666</v>
+        <v>45941.70833333334</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45941.58333333334</v>
+        <v>45941.72916666666</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.75</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45941.70833333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="105">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45941.72916666666</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45941.75</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="107">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="109">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,61 +15375,61 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -15442,10 +15442,10 @@
         </is>
       </c>
       <c r="AG116" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH116" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="117">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="118">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.875</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.91666666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="M120" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N120" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.9375</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.95833333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.97916666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,651 +16357,6 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45941.875</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="3" t="n">
-        <v>45941.91666666666</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M125" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N125" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="3" t="n">
-        <v>45941.9375</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="3" t="n">
-        <v>45941.95833333334</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" s="3" t="n">
-        <v>45941.97916666666</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>45941</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M128" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N128" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" s="3" t="n">
         <v>45941.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-11.xlsx
+++ b/jogos_2025-10-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45941.375</v>
+        <v>45941.35416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45941.39583333334</v>
+        <v>45941.375</v>
       </c>
     </row>
     <row r="18">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45941.41666666666</v>
+        <v>45941.39583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45941.4375</v>
+        <v>45941.41666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45941.45833333334</v>
+        <v>45941.4375</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>3.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.96</v>
+        <v>2.84</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N46" t="n">
-        <v>3.47</v>
+        <v>2.27</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>3.21</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.29</v>
+        <v>1.47</v>
       </c>
       <c r="M51" t="n">
-        <v>3.23</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,14 +7377,14 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.86</v>
+        <v>2.03</v>
       </c>
       <c r="M54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N54" t="n">
         <v>3.05</v>
       </c>
-      <c r="N54" t="n">
-        <v>2.26</v>
-      </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.03</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,49 +7764,49 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z57" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N57" t="n">
-        <v>4</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.93</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="M58" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="N58" t="n">
-        <v>5.8</v>
+        <v>1.61</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
         <v>3.37</v>
       </c>
       <c r="N59" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="N60" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="M61" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="N61" t="n">
-        <v>3.87</v>
+        <v>3.35</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="M64" t="n">
-        <v>3.37</v>
+        <v>3.02</v>
       </c>
       <c r="N64" t="n">
-        <v>3.62</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.84</v>
+        <v>1.84</v>
       </c>
       <c r="M65" t="n">
-        <v>3.07</v>
+        <v>3.33</v>
       </c>
       <c r="N65" t="n">
-        <v>2.27</v>
+        <v>3.62</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.57</v>
+        <v>1.96</v>
       </c>
       <c r="M67" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.5</v>
+        <v>3.47</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45941.46875</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45941.47916666666</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.45833333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.46875</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45941.5</v>
+        <v>45941.47916666666</v>
       </c>
     </row>
     <row r="76">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="83">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="84">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="85">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45941.52083333334</v>
+        <v>45941.5</v>
       </c>
     </row>
     <row r="86">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45941.53125</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45941.54166666666</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,27 +11980,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.52083333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.53125</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45941.5625</v>
+        <v>45941.54166666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45941.57291666666</v>
+        <v>45941.55208333334</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45941.58333333334</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45941.66666666666</v>
+        <v>45941.5625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45941.70833333334</v>
+        <v>45941.57291666666</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45941.72916666666</v>
+        <v>45941.58333333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45941.75</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.66666666666</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.70833333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.72916666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45941.79166666666</v>
+        <v>45941.75</v>
       </c>
     </row>
     <row r="107">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45941.83333333334</v>
+        <v>45941.79166666666</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,61 +15375,61 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -15442,10 +15442,10 @@
         </is>
       </c>
       <c r="AG116" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45941.85416666666</v>
+        <v>45941.83333333334</v>
       </c>
     </row>
     <row r="118">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45941.875</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45941.91666666666</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="M120" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N120" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45941.9375</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,61 +16020,61 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
@@ -16087,10 +16087,10 @@
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45941.95833333334</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,16 +16188,16 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45941.97916666666</v>
+        <v>45941.85416666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,126 +16237,771 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
+        <v>45941.875</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK124" s="3" t="n">
+        <v>45941.91666666666</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M125" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
+        <v>45941.9375</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="3" t="n">
+        <v>45941.95833333334</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>Las Vegas Lights</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Oakland Roots</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3" t="n">
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" s="3" t="n">
+        <v>45941.97916666666</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M128" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" s="3" t="n">
         <v>45941.97916666666</v>
       </c>
     </row>
